--- a/WTP_Power_Supply_and_Pump_Sizing.xlsx
+++ b/WTP_Power_Supply_and_Pump_Sizing.xlsx
@@ -9,10 +9,11 @@
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Inputs" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Pump Sizing" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Load Schedule" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Incoming Supply" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Pump Purchase Summary" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Inputs" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Pump Sizing" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Load Schedule" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Incoming Supply" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </workbook>
 </file>
 
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
     <author>Unknown Author</author>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="349">
   <si>
     <t xml:space="preserve">WTP 20 m3/h x 6 h/day - Power Supply and Pump Sizing Summary</t>
   </si>
@@ -177,6 +178,195 @@
     <t xml:space="preserve">Upper bound</t>
   </si>
   <si>
+    <t xml:space="preserve">Pump Purchase Summary - Number of Pumps to Procure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantities per drawing pump schedule (duty + standby). Motor kW and electrical data link to the Pump Sizing sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pump type / service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duty (nos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standby (nos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total to purchase (nos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flow each (m3/h)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motor kW (drawing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motor kW (calculated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motor kW (design)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supply</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Specification / remarks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A. PROCESS PUMPS (centrifugal, 415 V 3-phase, per drawing pump schedule)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raw Water Pump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-01 (duty), P-02 (standby)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415 V 3PH 50 Hz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End-suction centrifugal, SS304 impeller, cast iron casing, IP55 IE3 motor. Raw water duty - abrasion/solids tolerant. Suction from raw water tanks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backwash Pump (clean water)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-08 (duty), P-11 (standby)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End-suction centrifugal, SS304 wetted parts, IP55 IE3 motor. Draws from clarified water tank. Backwash tanks deleted - direct DN100 drain.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treated Water Pump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End-suction centrifugal, SS304/SS316 wetted parts (potable water, chlorinated), IP55 IE3 motor. Lifts to 3 x 45 m3 elevated tanks at 7.0 m. NOTE: no standby shown on drawing - recommend adding 1 standby (see row 4).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treated Water Pump - recommended standby (OPTIONAL, not on drawing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-09S (proposed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treated water pump is the only single point of failure feeding the elevated tanks. Set standby qty to 0 to exclude. If purchased, add one MCC feeder (25 A MCCB, Star-Delta) and recheck incoming supply.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subtotal - process pumps (per drawing, rows 1-3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Installed motor kW = sum of (qty x design kW)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subtotal - process pumps incl. optional standby (rows 1-4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B. CHEMICAL DOSING PUMPS (diaphragm metering, from Chemical Dosing Area)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAC dosing pump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240 V 1PH 50 Hz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAC (poly aluminium chloride) coagulant, dosed after soda ash before static mixer / rapid mix. Solenoid or motor-driven diaphragm, PVDF/PTFE head, approx. 0-10 L/h at 7 bar (confirm from jar test dose rate).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soda Ash dosing pump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soda ash (Na2CO3) for pH/alkalinity, first dosing point on DN90 raw water line. Diaphragm, PP/PVDF head, approx. 0-10 L/h at 7 bar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCCA (chlorine) dosing pump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCCA solution, dosed downstream of CP-03 on DN90 rising main before elevated tanks. Diaphragm, PVDF/PTFE/Viton wetted parts, approx. 0-5 L/h at 7 bar. Residual chlorine sample tap required.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C833 / HEDP dosing pump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antiscalant/HEDP after sand filter and treated water pump. Separate quill. ONLY if SDS/COA approved - hold purchase until approval. Diaphragm, PVDF head, approx. 0-5 L/h at 7 bar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spare dosing pump (common spare, OPTIONAL)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One shelf spare covering all four chemicals (same frame size, swap head/diaphragm per chemical). Set to 0 to exclude.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subtotal - dosing pumps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C. GRAND TOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total pumps to purchase - as per drawing (no optional items)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 process pumps + 4 dosing pumps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total pumps to purchase - including optional standby and spare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjust the yellow quantity cells to include or exclude optional items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total installed process-pump motor kW (as per drawing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Quantities for process pumps follow the drawing pump schedule: 2 raw water (1 duty + 1 standby), 2 backwash (1 duty + 1 standby), 1 treated water. Backwash tanks 10A/10B are deleted; the backwash pump draws from the clarified water tank.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. The drawing specifies 5.5 kW motors for all five process pumps. Hydraulic calculation gives 2.2 kW for raw and treated water pumps and 5.5 kW for backwash pumps. Purchase to the drawing unless the vendor confirms a smaller motor on the selected pump curve.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Specify duty point (flow and head), NPSH available, liquid (raw water with solids vs treated chlorinated water), and material of wetted parts in the purchase order. Request pump curves and motor nameplate data to update the Inputs sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Dosing pump capacities are indicative. Final L/h rating comes from dose rate (mg/L) x 20 m3/h x stock solution concentration. Order with pulsation dampener, back-pressure valve, injection quill and calibration column for each.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Agitators (4 nos, chemical tanks) are not pumps and are excluded from this list; see Load Schedule DB-4.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Water Treatment Plant 20 m3/h - Electrical Design Inputs</t>
   </si>
   <si>
@@ -234,9 +424,6 @@
     <t xml:space="preserve">Motor power factor at full load</t>
   </si>
   <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
     <t xml:space="preserve">Typical IE3 4-pole 5.5 kW motor at full load. Confirm from motor nameplate.</t>
   </si>
   <si>
@@ -390,9 +577,6 @@
     <t xml:space="preserve">P_hyd (kW) = rho x g x Q x H / (3,600 x 1,000).  Shaft kW = P_hyd / pump eff.  Motor = next standard IEC rating above shaft kW x margin.</t>
   </si>
   <si>
-    <t xml:space="preserve">No.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tag</t>
   </si>
   <si>
@@ -438,9 +622,6 @@
     <t xml:space="preserve">FLC (A)</t>
   </si>
   <si>
-    <t xml:space="preserve">Starter</t>
-  </si>
-  <si>
     <t xml:space="preserve">Starting current (A)</t>
   </si>
   <si>
@@ -489,12 +670,6 @@
     <t xml:space="preserve">Identical to P-08, 100% standby.</t>
   </si>
   <si>
-    <t xml:space="preserve">P-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Treated Water Pump</t>
-  </si>
-  <si>
     <t xml:space="preserve">Drawing: 10-12 m3/h, 25-30 m. Lifts to elevated tanks at 7.0 m plus DN90 rising main losses.</t>
   </si>
   <si>
@@ -505,9 +680,6 @@
   </si>
   <si>
     <t xml:space="preserve">Largest single motor (kW)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOTES</t>
   </si>
   <si>
     <t xml:space="preserve">1. Hydraulic power uses the upper end of the flow and head ranges on the drawing, which is conservative.</t>
@@ -932,14 +1104,14 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="General"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
-    <numFmt numFmtId="170" formatCode="0.00"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="0.00"/>
+    <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="170" formatCode="0.0%"/>
     <numFmt numFmtId="171" formatCode="0"/>
     <numFmt numFmtId="172" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1012,13 +1184,20 @@
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <b val="true"/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
+      <i val="true"/>
       <sz val="9"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -1111,9 +1290,41 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="51">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -1122,10 +1333,6 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -1137,10 +1344,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1148,15 +1351,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1164,11 +1367,51 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1180,43 +1423,35 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1232,11 +1467,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1244,7 +1475,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1252,7 +1483,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1519,331 +1750,331 @@
   <dimension ref="A1:D26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="8" t="n">
         <f aca="false">'Pump Sizing'!K5</f>
         <v>2.2</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="8" t="n">
         <f aca="false">'Pump Sizing'!L5</f>
         <v>5.5</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="6"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="D7" s="7"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="8" t="n">
         <f aca="false">'Pump Sizing'!K7</f>
         <v>5.5</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="8" t="n">
         <f aca="false">'Pump Sizing'!L7</f>
         <v>5.5</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="6"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+      <c r="D9" s="7"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="8" t="n">
         <f aca="false">'Pump Sizing'!K9</f>
         <v>2.2</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="8" t="n">
         <f aca="false">'Pump Sizing'!L9</f>
         <v>5.5</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="6"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+      <c r="D11" s="7"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="8" t="n">
         <f aca="false">'Pump Sizing'!M11</f>
         <v>27.5</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="8" t="n">
         <f aca="false">'Pump Sizing'!P5</f>
         <v>10.0467831848706</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="6"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+      <c r="D13" s="7"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="8" t="n">
         <f aca="false">'Load Schedule'!Q5</f>
         <v>25</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="8" t="n">
         <f aca="false">'Load Schedule'!V5</f>
         <v>2.5</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="7" t="n">
+      <c r="B17" s="8" t="n">
         <f aca="false">'Incoming Supply'!B6</f>
         <v>33.96</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="6"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+      <c r="D17" s="7"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="7" t="n">
+      <c r="B18" s="8" t="n">
         <f aca="false">'Incoming Supply'!B8</f>
         <v>27.9051120448179</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="7" t="n">
+      <c r="B19" s="8" t="n">
         <f aca="false">'Incoming Supply'!B10</f>
         <v>38.821744459861</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="6"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
+      <c r="D19" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="7" t="n">
+      <c r="B20" s="8" t="n">
         <f aca="false">'Incoming Supply'!B13</f>
         <v>48.5271805748262</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="6"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
+      <c r="D20" s="7"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="7" t="n">
+      <c r="B21" s="8" t="n">
         <f aca="false">'Incoming Supply'!B21</f>
         <v>63</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="7" t="n">
+      <c r="B22" s="8" t="n">
         <f aca="false">'Incoming Supply'!B19</f>
         <v>225</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="7" t="n">
+      <c r="B23" s="8" t="n">
         <f aca="false">'Incoming Supply'!B26</f>
         <v>16</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="7" t="n">
+      <c r="B24" s="8" t="n">
         <f aca="false">'Incoming Supply'!B33</f>
         <v>35</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="6"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
+      <c r="D24" s="7"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="7" t="n">
+      <c r="B25" s="8" t="n">
         <f aca="false">'Incoming Supply'!B43</f>
         <v>40</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D25" s="6"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
+      <c r="D25" s="7"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="7" t="n">
+      <c r="B26" s="8" t="n">
         <f aca="false">'Incoming Supply'!B36</f>
         <v>4302.48214285714</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="7" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1863,673 +2094,685 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="48"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="9" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+    </row>
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <f aca="false">D6+E6</f>
+        <v>2</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <f aca="false">'Pump Sizing'!E5</f>
+        <v>10</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <f aca="false">'Pump Sizing'!F5</f>
+        <v>30</v>
+      </c>
+      <c r="I6" s="16" t="n">
+        <f aca="false">'Pump Sizing'!L5</f>
+        <v>5.5</v>
+      </c>
+      <c r="J6" s="16" t="n">
+        <f aca="false">'Pump Sizing'!K5</f>
+        <v>2.2</v>
+      </c>
+      <c r="K6" s="16" t="n">
+        <f aca="false">'Pump Sizing'!M5</f>
+        <v>5.5</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="M6" s="17" t="str">
+        <f aca="false">'Pump Sizing'!Q5</f>
+        <v>Star-Delta</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <f aca="false">D7+E7</f>
+        <v>2</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <f aca="false">'Pump Sizing'!E7</f>
+        <v>30</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <f aca="false">'Pump Sizing'!F7</f>
+        <v>30</v>
+      </c>
+      <c r="I7" s="16" t="n">
+        <f aca="false">'Pump Sizing'!L7</f>
+        <v>5.5</v>
+      </c>
+      <c r="J7" s="16" t="n">
+        <f aca="false">'Pump Sizing'!K7</f>
+        <v>5.5</v>
+      </c>
+      <c r="K7" s="16" t="n">
+        <f aca="false">'Pump Sizing'!M7</f>
+        <v>5.5</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="M7" s="17" t="str">
+        <f aca="false">'Pump Sizing'!Q7</f>
+        <v>Star-Delta</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="B8" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <f aca="false">D8+E8</f>
+        <v>1</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <f aca="false">'Pump Sizing'!E9</f>
+        <v>12</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <f aca="false">'Pump Sizing'!F9</f>
+        <v>30</v>
+      </c>
+      <c r="I8" s="16" t="n">
+        <f aca="false">'Pump Sizing'!L9</f>
+        <v>5.5</v>
+      </c>
+      <c r="J8" s="16" t="n">
+        <f aca="false">'Pump Sizing'!K9</f>
+        <v>2.2</v>
+      </c>
+      <c r="K8" s="16" t="n">
+        <f aca="false">'Pump Sizing'!M9</f>
+        <v>5.5</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="M8" s="17" t="str">
+        <f aca="false">'Pump Sizing'!Q9</f>
+        <v>Star-Delta</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="F5" s="8" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="H5" s="8" t="n">
+      <c r="B9" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <f aca="false">D9+E9</f>
+        <v>1</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <f aca="false">'Pump Sizing'!E9</f>
+        <v>12</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <f aca="false">'Pump Sizing'!F9</f>
+        <v>30</v>
+      </c>
+      <c r="I9" s="16" t="n">
+        <f aca="false">'Pump Sizing'!L9</f>
+        <v>5.5</v>
+      </c>
+      <c r="J9" s="16" t="n">
+        <f aca="false">'Pump Sizing'!K9</f>
+        <v>2.2</v>
+      </c>
+      <c r="K9" s="16" t="n">
+        <f aca="false">'Pump Sizing'!M9</f>
+        <v>5.5</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="M9" s="17" t="str">
+        <f aca="false">'Pump Sizing'!Q9</f>
+        <v>Star-Delta</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="20" t="n">
+        <f aca="false">SUM(D6:D8)</f>
+        <v>3</v>
+      </c>
+      <c r="E10" s="20" t="n">
+        <f aca="false">SUM(E6:E8)</f>
+        <v>2</v>
+      </c>
+      <c r="F10" s="20" t="n">
+        <f aca="false">SUM(F6:F8)</f>
+        <v>5</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <f aca="false">SUMPRODUCT(F6:F8,K6:K8)</f>
+        <v>27.5</v>
+      </c>
+      <c r="N10" s="22" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="20" t="n">
+        <f aca="false">SUM(D6:D9)</f>
+        <v>3</v>
+      </c>
+      <c r="E11" s="20" t="n">
+        <f aca="false">SUM(E6:E9)</f>
+        <v>3</v>
+      </c>
+      <c r="F11" s="20" t="n">
+        <f aca="false">SUM(F6:F9)</f>
         <v>6</v>
       </c>
-      <c r="J5" s="8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K5" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="L5" s="8" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="8" t="n">
-        <v>415</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="H6" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="J6" s="8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K6" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="L6" s="8" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="J7" s="8" t="n">
+      <c r="K11" s="21" t="n">
+        <f aca="false">SUMPRODUCT(F6:F9,K6:K9)</f>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+    </row>
+    <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <f aca="false">D14+E14</f>
+        <v>1</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="K14" s="23" t="n">
+        <f aca="false">'Load Schedule'!F12</f>
+        <v>0.12</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <f aca="false">D15+E15</f>
+        <v>1</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="K15" s="23" t="n">
+        <f aca="false">'Load Schedule'!F12</f>
+        <v>0.12</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <f aca="false">D16+E16</f>
+        <v>1</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="K16" s="23" t="n">
+        <f aca="false">'Load Schedule'!F12</f>
+        <v>0.12</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <f aca="false">D17+E17</f>
+        <v>1</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="K17" s="23" t="n">
+        <f aca="false">'Load Schedule'!F12</f>
+        <v>0.12</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <f aca="false">D18+E18</f>
+        <v>1</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="K18" s="23" t="n">
+        <f aca="false">'Load Schedule'!F12</f>
+        <v>0.12</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" s="20" t="n">
+        <f aca="false">SUM(D14:D18)</f>
         <v>4</v>
       </c>
-      <c r="K7" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="L7" s="8" t="n">
+      <c r="E19" s="20" t="n">
+        <f aca="false">SUM(E14:E18)</f>
+        <v>1</v>
+      </c>
+      <c r="F19" s="20" t="n">
+        <f aca="false">SUM(F14:F18)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="F22" s="24" t="n">
+        <f aca="false">F10+SUM(F14:F17)</f>
+        <v>9</v>
+      </c>
+      <c r="N22" s="22" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="F23" s="24" t="n">
+        <f aca="false">F11+F19</f>
         <v>11</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="9" t="n">
-        <f aca="false">ROUND(B6/SQRT(3),0)</f>
-        <v>240</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="J8" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="K8" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="L8" s="8" t="n">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9" s="10" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="J9" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="K9" s="8" t="n">
-        <v>71</v>
-      </c>
-      <c r="L9" s="8" t="n">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" s="10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="J10" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="K10" s="8" t="n">
-        <v>94</v>
-      </c>
-      <c r="L10" s="8" t="n">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B11" s="11" t="n">
-        <v>0.896</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="J11" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="K11" s="8" t="n">
-        <v>124</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B12" s="10" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="J12" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="K12" s="8" t="n">
-        <v>153</v>
-      </c>
-      <c r="L12" s="8" t="n">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B13" s="12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>63</v>
-      </c>
-      <c r="J13" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="K13" s="8" t="n">
-        <v>185</v>
-      </c>
-      <c r="L13" s="8" t="n">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B14" s="8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>80</v>
-      </c>
-      <c r="J14" s="8" t="n">
-        <v>70</v>
-      </c>
-      <c r="K14" s="8" t="n">
-        <v>236</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B15" s="8" t="n">
-        <v>9.81</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" s="6"/>
-      <c r="F15" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="H15" s="8" t="n">
+      <c r="N23" s="22" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="K24" s="21" t="n">
+        <f aca="false">K10</f>
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="J15" s="8" t="n">
-        <v>95</v>
-      </c>
-      <c r="K15" s="8" t="n">
-        <v>288</v>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="F16" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="J16" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="K16" s="8" t="n">
-        <v>335</v>
-      </c>
-      <c r="L16" s="8" t="n">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B17" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>160</v>
-      </c>
-      <c r="J17" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="K17" s="8" t="n">
-        <v>385</v>
-      </c>
-      <c r="L17" s="8" t="n">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B18" s="8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="J18" s="8" t="n">
-        <v>185</v>
-      </c>
-      <c r="K18" s="8" t="n">
-        <v>440</v>
-      </c>
-      <c r="L18" s="8" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="B19" s="10" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="F19" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>225</v>
-      </c>
-      <c r="J19" s="8" t="n">
-        <v>240</v>
-      </c>
-      <c r="K19" s="8" t="n">
-        <v>515</v>
-      </c>
-      <c r="L19" s="8" t="n">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="B20" s="13" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="B21" s="13" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>320</v>
-      </c>
-      <c r="J21" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B22" s="10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H22" s="8" t="n">
-        <v>400</v>
-      </c>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
-    </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="B23" s="10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="B24" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B25" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="B26" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B27" s="15" t="s">
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D27" s="6" t="s">
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="26" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="B29" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B30" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="B31" s="10" t="n">
-        <v>0.509</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>111</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="J21:L24"/>
-  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2545,507 +2788,673 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="10" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="K4" s="4" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="L4" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B4" s="3" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="F5" s="14" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="L5" s="14" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="B6" s="14" t="n">
+        <v>415</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="D6" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F6" s="14" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K6" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="L6" s="14" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="B7" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="D7" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="F7" s="14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="L7" s="14" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="B8" s="13" t="n">
+        <f aca="false">ROUND(B6/SQRT(3),0)</f>
+        <v>240</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="F8" s="14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="K8" s="14" t="n">
+        <v>52</v>
+      </c>
+      <c r="L8" s="14" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="B9" s="27" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="F9" s="14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>71</v>
+      </c>
+      <c r="L9" s="14" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="B10" s="27" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="F10" s="14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="K10" s="14" t="n">
+        <v>94</v>
+      </c>
+      <c r="L10" s="14" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="B11" s="28" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="F11" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <v>124</v>
+      </c>
+      <c r="L11" s="14" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="B12" s="27" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="F12" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="K12" s="14" t="n">
+        <v>153</v>
+      </c>
+      <c r="L12" s="14" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="6" t="s">
+      <c r="B13" s="18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="F13" s="14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>63</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="K13" s="14" t="n">
+        <v>185</v>
+      </c>
+      <c r="L13" s="14" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="B14" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="E5" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="F5" s="17" t="n">
+      <c r="D14" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="K14" s="14" t="n">
+        <v>236</v>
+      </c>
+      <c r="L14" s="14" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="F15" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="J15" s="14" t="n">
+        <v>95</v>
+      </c>
+      <c r="K15" s="14" t="n">
+        <v>288</v>
+      </c>
+      <c r="L15" s="14" t="n">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="F16" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>125</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="K16" s="14" t="n">
+        <v>335</v>
+      </c>
+      <c r="L16" s="14" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B17" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>160</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="K17" s="14" t="n">
+        <v>385</v>
+      </c>
+      <c r="L17" s="14" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B18" s="14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>185</v>
+      </c>
+      <c r="K18" s="14" t="n">
+        <v>440</v>
+      </c>
+      <c r="L18" s="14" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B19" s="27" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="F19" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="G5" s="18" t="n">
-        <f aca="false">Inputs!$B$14*Inputs!$B$15*E5*F5/(3600*1000)</f>
-        <v>0.8175</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <f aca="false">Inputs!$B$12</f>
-        <v>0.65</v>
-      </c>
-      <c r="I5" s="18" t="n">
-        <f aca="false">G5/H5</f>
-        <v>1.25769230769231</v>
-      </c>
-      <c r="J5" s="18" t="n">
-        <f aca="false">I5*Inputs!$B$13</f>
-        <v>1.50923076923077</v>
-      </c>
-      <c r="K5" s="18" t="n">
-        <f aca="false">INDEX(Inputs!$F$5:$F$19,COUNTIF(Inputs!$F$5:$F$19,"&lt;"&amp;J5)+1)</f>
-        <v>2.2</v>
-      </c>
-      <c r="L5" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="M5" s="18" t="n">
-        <f aca="false">IF(Inputs!$B$27="Calculated",K5,L5)</f>
-        <v>5.5</v>
-      </c>
-      <c r="N5" s="20" t="n">
-        <f aca="false">Inputs!$B$11</f>
-        <v>0.896</v>
-      </c>
-      <c r="O5" s="19" t="n">
-        <f aca="false">Inputs!$B$9</f>
-        <v>0.85</v>
-      </c>
-      <c r="P5" s="21" t="n">
-        <f aca="false">M5*1000/(SQRT(3)*Inputs!$B$6*N5*O5)</f>
-        <v>10.0467831848706</v>
-      </c>
-      <c r="Q5" s="9" t="str">
-        <f aca="false">IF(M5&gt;=Inputs!$B$26,"Star-Delta","DOL")</f>
-        <v>Star-Delta</v>
-      </c>
-      <c r="R5" s="21" t="n">
-        <f aca="false">P5*IF(Q5="DOL",Inputs!$B$24,Inputs!$B$25)</f>
-        <v>20.0935663697412</v>
-      </c>
-      <c r="S5" s="6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="n">
+      <c r="H19" s="14" t="n">
+        <v>225</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>240</v>
+      </c>
+      <c r="K19" s="14" t="n">
+        <v>515</v>
+      </c>
+      <c r="L19" s="14" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B20" s="29" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B21" s="29" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>320</v>
+      </c>
+      <c r="J21" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="K21" s="30"/>
+      <c r="L21" s="30"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B22" s="27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>400</v>
+      </c>
+      <c r="J22" s="30"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="30"/>
+    </row>
+    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="B23" s="27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="B24" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="B25" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="E6" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="F6" s="17" t="n">
+      <c r="C25" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="B26" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B27" s="31" t="s">
+        <v>163</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="B29" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B30" s="18" t="n">
         <v>30</v>
       </c>
-      <c r="G6" s="18" t="n">
-        <f aca="false">Inputs!$B$14*Inputs!$B$15*E6*F6/(3600*1000)</f>
-        <v>0.8175</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <f aca="false">Inputs!$B$12</f>
-        <v>0.65</v>
-      </c>
-      <c r="I6" s="18" t="n">
-        <f aca="false">G6/H6</f>
-        <v>1.25769230769231</v>
-      </c>
-      <c r="J6" s="18" t="n">
-        <f aca="false">I6*Inputs!$B$13</f>
-        <v>1.50923076923077</v>
-      </c>
-      <c r="K6" s="18" t="n">
-        <f aca="false">INDEX(Inputs!$F$5:$F$19,COUNTIF(Inputs!$F$5:$F$19,"&lt;"&amp;J6)+1)</f>
-        <v>2.2</v>
-      </c>
-      <c r="L6" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="M6" s="18" t="n">
-        <f aca="false">IF(Inputs!$B$27="Calculated",K6,L6)</f>
-        <v>5.5</v>
-      </c>
-      <c r="N6" s="20" t="n">
-        <f aca="false">Inputs!$B$11</f>
-        <v>0.896</v>
-      </c>
-      <c r="O6" s="19" t="n">
-        <f aca="false">Inputs!$B$9</f>
-        <v>0.85</v>
-      </c>
-      <c r="P6" s="21" t="n">
-        <f aca="false">M6*1000/(SQRT(3)*Inputs!$B$6*N6*O6)</f>
-        <v>10.0467831848706</v>
-      </c>
-      <c r="Q6" s="9" t="str">
-        <f aca="false">IF(M6&gt;=Inputs!$B$26,"Star-Delta","DOL")</f>
-        <v>Star-Delta</v>
-      </c>
-      <c r="R6" s="21" t="n">
-        <f aca="false">P6*IF(Q6="DOL",Inputs!$B$24,Inputs!$B$25)</f>
-        <v>20.0935663697412</v>
-      </c>
-      <c r="S6" s="6" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="E7" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="F7" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="G7" s="18" t="n">
-        <f aca="false">Inputs!$B$14*Inputs!$B$15*E7*F7/(3600*1000)</f>
-        <v>2.4525</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <f aca="false">Inputs!$B$12</f>
-        <v>0.65</v>
-      </c>
-      <c r="I7" s="18" t="n">
-        <f aca="false">G7/H7</f>
-        <v>3.77307692307692</v>
-      </c>
-      <c r="J7" s="18" t="n">
-        <f aca="false">I7*Inputs!$B$13</f>
-        <v>4.52769230769231</v>
-      </c>
-      <c r="K7" s="18" t="n">
-        <f aca="false">INDEX(Inputs!$F$5:$F$19,COUNTIF(Inputs!$F$5:$F$19,"&lt;"&amp;J7)+1)</f>
-        <v>5.5</v>
-      </c>
-      <c r="L7" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="M7" s="18" t="n">
-        <f aca="false">IF(Inputs!$B$27="Calculated",K7,L7)</f>
-        <v>5.5</v>
-      </c>
-      <c r="N7" s="20" t="n">
-        <f aca="false">Inputs!$B$11</f>
-        <v>0.896</v>
-      </c>
-      <c r="O7" s="19" t="n">
-        <f aca="false">Inputs!$B$9</f>
-        <v>0.85</v>
-      </c>
-      <c r="P7" s="21" t="n">
-        <f aca="false">M7*1000/(SQRT(3)*Inputs!$B$6*N7*O7)</f>
-        <v>10.0467831848706</v>
-      </c>
-      <c r="Q7" s="9" t="str">
-        <f aca="false">IF(M7&gt;=Inputs!$B$26,"Star-Delta","DOL")</f>
-        <v>Star-Delta</v>
-      </c>
-      <c r="R7" s="21" t="n">
-        <f aca="false">P7*IF(Q7="DOL",Inputs!$B$24,Inputs!$B$25)</f>
-        <v>20.0935663697412</v>
-      </c>
-      <c r="S7" s="6" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="F8" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="G8" s="18" t="n">
-        <f aca="false">Inputs!$B$14*Inputs!$B$15*E8*F8/(3600*1000)</f>
-        <v>2.4525</v>
-      </c>
-      <c r="H8" s="19" t="n">
-        <f aca="false">Inputs!$B$12</f>
-        <v>0.65</v>
-      </c>
-      <c r="I8" s="18" t="n">
-        <f aca="false">G8/H8</f>
-        <v>3.77307692307692</v>
-      </c>
-      <c r="J8" s="18" t="n">
-        <f aca="false">I8*Inputs!$B$13</f>
-        <v>4.52769230769231</v>
-      </c>
-      <c r="K8" s="18" t="n">
-        <f aca="false">INDEX(Inputs!$F$5:$F$19,COUNTIF(Inputs!$F$5:$F$19,"&lt;"&amp;J8)+1)</f>
-        <v>5.5</v>
-      </c>
-      <c r="L8" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="M8" s="18" t="n">
-        <f aca="false">IF(Inputs!$B$27="Calculated",K8,L8)</f>
-        <v>5.5</v>
-      </c>
-      <c r="N8" s="20" t="n">
-        <f aca="false">Inputs!$B$11</f>
-        <v>0.896</v>
-      </c>
-      <c r="O8" s="19" t="n">
-        <f aca="false">Inputs!$B$9</f>
-        <v>0.85</v>
-      </c>
-      <c r="P8" s="21" t="n">
-        <f aca="false">M8*1000/(SQRT(3)*Inputs!$B$6*N8*O8)</f>
-        <v>10.0467831848706</v>
-      </c>
-      <c r="Q8" s="9" t="str">
-        <f aca="false">IF(M8&gt;=Inputs!$B$26,"Star-Delta","DOL")</f>
-        <v>Star-Delta</v>
-      </c>
-      <c r="R8" s="21" t="n">
-        <f aca="false">P8*IF(Q8="DOL",Inputs!$B$24,Inputs!$B$25)</f>
-        <v>20.0935663697412</v>
-      </c>
-      <c r="S8" s="6" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="E9" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="F9" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="G9" s="18" t="n">
-        <f aca="false">Inputs!$B$14*Inputs!$B$15*E9*F9/(3600*1000)</f>
-        <v>0.981</v>
-      </c>
-      <c r="H9" s="19" t="n">
-        <f aca="false">Inputs!$B$12</f>
-        <v>0.65</v>
-      </c>
-      <c r="I9" s="18" t="n">
-        <f aca="false">G9/H9</f>
-        <v>1.50923076923077</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <f aca="false">I9*Inputs!$B$13</f>
-        <v>1.81107692307692</v>
-      </c>
-      <c r="K9" s="18" t="n">
-        <f aca="false">INDEX(Inputs!$F$5:$F$19,COUNTIF(Inputs!$F$5:$F$19,"&lt;"&amp;J9)+1)</f>
-        <v>2.2</v>
-      </c>
-      <c r="L9" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="M9" s="18" t="n">
-        <f aca="false">IF(Inputs!$B$27="Calculated",K9,L9)</f>
-        <v>5.5</v>
-      </c>
-      <c r="N9" s="20" t="n">
-        <f aca="false">Inputs!$B$11</f>
-        <v>0.896</v>
-      </c>
-      <c r="O9" s="19" t="n">
-        <f aca="false">Inputs!$B$9</f>
-        <v>0.85</v>
-      </c>
-      <c r="P9" s="21" t="n">
-        <f aca="false">M9*1000/(SQRT(3)*Inputs!$B$6*N9*O9)</f>
-        <v>10.0467831848706</v>
-      </c>
-      <c r="Q9" s="9" t="str">
-        <f aca="false">IF(M9&gt;=Inputs!$B$26,"Star-Delta","DOL")</f>
-        <v>Star-Delta</v>
-      </c>
-      <c r="R9" s="21" t="n">
-        <f aca="false">P9*IF(Q9="DOL",Inputs!$B$24,Inputs!$B$25)</f>
-        <v>20.0935663697412</v>
-      </c>
-      <c r="S9" s="6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="M11" s="23" t="n">
-        <f aca="false">SUM(M5:M9)</f>
-        <v>27.5</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C12" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="M12" s="23" t="n">
-        <f aca="false">SUMIF(D5:D9,"Duty",M5:M9)</f>
-        <v>16.5</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="M13" s="23" t="n">
-        <f aca="false">MAX(M5:M9)</f>
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="24" t="s">
+      <c r="C30" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="25" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="25" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="25" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="25" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="25" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="25" t="s">
-        <v>159</v>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B31" s="27" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>173</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="J21:L24"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -3061,1239 +3470,1755 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
+  <dimension ref="A1:S21"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="10" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="E5" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="33" t="n">
+        <v>30</v>
+      </c>
+      <c r="G5" s="34" t="n">
+        <f aca="false">Inputs!$B$14*Inputs!$B$15*E5*F5/(3600*1000)</f>
+        <v>0.8175</v>
+      </c>
+      <c r="H5" s="23" t="n">
+        <f aca="false">Inputs!$B$12</f>
+        <v>0.65</v>
+      </c>
+      <c r="I5" s="34" t="n">
+        <f aca="false">G5/H5</f>
+        <v>1.25769230769231</v>
+      </c>
+      <c r="J5" s="34" t="n">
+        <f aca="false">I5*Inputs!$B$13</f>
+        <v>1.50923076923077</v>
+      </c>
+      <c r="K5" s="34" t="n">
+        <f aca="false">INDEX(Inputs!$F$5:$F$19,COUNTIF(Inputs!$F$5:$F$19,"&lt;"&amp;J5)+1)</f>
+        <v>2.2</v>
+      </c>
+      <c r="L5" s="33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M5" s="34" t="n">
+        <f aca="false">IF(Inputs!$B$27="Calculated",K5,L5)</f>
+        <v>5.5</v>
+      </c>
+      <c r="N5" s="35" t="n">
+        <f aca="false">Inputs!$B$11</f>
+        <v>0.896</v>
+      </c>
+      <c r="O5" s="23" t="n">
+        <f aca="false">Inputs!$B$9</f>
+        <v>0.85</v>
+      </c>
+      <c r="P5" s="36" t="n">
+        <f aca="false">M5*1000/(SQRT(3)*Inputs!$B$6*N5*O5)</f>
+        <v>10.0467831848706</v>
+      </c>
+      <c r="Q5" s="13" t="str">
+        <f aca="false">IF(M5&gt;=Inputs!$B$26,"Star-Delta","DOL")</f>
+        <v>Star-Delta</v>
+      </c>
+      <c r="R5" s="36" t="n">
+        <f aca="false">P5*IF(Q5="DOL",Inputs!$B$24,Inputs!$B$25)</f>
+        <v>20.0935663697412</v>
+      </c>
+      <c r="S5" s="7" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="E6" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="33" t="n">
+        <v>30</v>
+      </c>
+      <c r="G6" s="34" t="n">
+        <f aca="false">Inputs!$B$14*Inputs!$B$15*E6*F6/(3600*1000)</f>
+        <v>0.8175</v>
+      </c>
+      <c r="H6" s="23" t="n">
+        <f aca="false">Inputs!$B$12</f>
+        <v>0.65</v>
+      </c>
+      <c r="I6" s="34" t="n">
+        <f aca="false">G6/H6</f>
+        <v>1.25769230769231</v>
+      </c>
+      <c r="J6" s="34" t="n">
+        <f aca="false">I6*Inputs!$B$13</f>
+        <v>1.50923076923077</v>
+      </c>
+      <c r="K6" s="34" t="n">
+        <f aca="false">INDEX(Inputs!$F$5:$F$19,COUNTIF(Inputs!$F$5:$F$19,"&lt;"&amp;J6)+1)</f>
+        <v>2.2</v>
+      </c>
+      <c r="L6" s="33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M6" s="34" t="n">
+        <f aca="false">IF(Inputs!$B$27="Calculated",K6,L6)</f>
+        <v>5.5</v>
+      </c>
+      <c r="N6" s="35" t="n">
+        <f aca="false">Inputs!$B$11</f>
+        <v>0.896</v>
+      </c>
+      <c r="O6" s="23" t="n">
+        <f aca="false">Inputs!$B$9</f>
+        <v>0.85</v>
+      </c>
+      <c r="P6" s="36" t="n">
+        <f aca="false">M6*1000/(SQRT(3)*Inputs!$B$6*N6*O6)</f>
+        <v>10.0467831848706</v>
+      </c>
+      <c r="Q6" s="13" t="str">
+        <f aca="false">IF(M6&gt;=Inputs!$B$26,"Star-Delta","DOL")</f>
+        <v>Star-Delta</v>
+      </c>
+      <c r="R6" s="36" t="n">
+        <f aca="false">P6*IF(Q6="DOL",Inputs!$B$24,Inputs!$B$25)</f>
+        <v>20.0935663697412</v>
+      </c>
+      <c r="S6" s="7" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="E7" s="33" t="n">
+        <v>30</v>
+      </c>
+      <c r="F7" s="33" t="n">
+        <v>30</v>
+      </c>
+      <c r="G7" s="34" t="n">
+        <f aca="false">Inputs!$B$14*Inputs!$B$15*E7*F7/(3600*1000)</f>
+        <v>2.4525</v>
+      </c>
+      <c r="H7" s="23" t="n">
+        <f aca="false">Inputs!$B$12</f>
+        <v>0.65</v>
+      </c>
+      <c r="I7" s="34" t="n">
+        <f aca="false">G7/H7</f>
+        <v>3.77307692307692</v>
+      </c>
+      <c r="J7" s="34" t="n">
+        <f aca="false">I7*Inputs!$B$13</f>
+        <v>4.52769230769231</v>
+      </c>
+      <c r="K7" s="34" t="n">
+        <f aca="false">INDEX(Inputs!$F$5:$F$19,COUNTIF(Inputs!$F$5:$F$19,"&lt;"&amp;J7)+1)</f>
+        <v>5.5</v>
+      </c>
+      <c r="L7" s="33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M7" s="34" t="n">
+        <f aca="false">IF(Inputs!$B$27="Calculated",K7,L7)</f>
+        <v>5.5</v>
+      </c>
+      <c r="N7" s="35" t="n">
+        <f aca="false">Inputs!$B$11</f>
+        <v>0.896</v>
+      </c>
+      <c r="O7" s="23" t="n">
+        <f aca="false">Inputs!$B$9</f>
+        <v>0.85</v>
+      </c>
+      <c r="P7" s="36" t="n">
+        <f aca="false">M7*1000/(SQRT(3)*Inputs!$B$6*N7*O7)</f>
+        <v>10.0467831848706</v>
+      </c>
+      <c r="Q7" s="13" t="str">
+        <f aca="false">IF(M7&gt;=Inputs!$B$26,"Star-Delta","DOL")</f>
+        <v>Star-Delta</v>
+      </c>
+      <c r="R7" s="36" t="n">
+        <f aca="false">P7*IF(Q7="DOL",Inputs!$B$24,Inputs!$B$25)</f>
+        <v>20.0935663697412</v>
+      </c>
+      <c r="S7" s="7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="E8" s="33" t="n">
+        <v>30</v>
+      </c>
+      <c r="F8" s="33" t="n">
+        <v>30</v>
+      </c>
+      <c r="G8" s="34" t="n">
+        <f aca="false">Inputs!$B$14*Inputs!$B$15*E8*F8/(3600*1000)</f>
+        <v>2.4525</v>
+      </c>
+      <c r="H8" s="23" t="n">
+        <f aca="false">Inputs!$B$12</f>
+        <v>0.65</v>
+      </c>
+      <c r="I8" s="34" t="n">
+        <f aca="false">G8/H8</f>
+        <v>3.77307692307692</v>
+      </c>
+      <c r="J8" s="34" t="n">
+        <f aca="false">I8*Inputs!$B$13</f>
+        <v>4.52769230769231</v>
+      </c>
+      <c r="K8" s="34" t="n">
+        <f aca="false">INDEX(Inputs!$F$5:$F$19,COUNTIF(Inputs!$F$5:$F$19,"&lt;"&amp;J8)+1)</f>
+        <v>5.5</v>
+      </c>
+      <c r="L8" s="33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M8" s="34" t="n">
+        <f aca="false">IF(Inputs!$B$27="Calculated",K8,L8)</f>
+        <v>5.5</v>
+      </c>
+      <c r="N8" s="35" t="n">
+        <f aca="false">Inputs!$B$11</f>
+        <v>0.896</v>
+      </c>
+      <c r="O8" s="23" t="n">
+        <f aca="false">Inputs!$B$9</f>
+        <v>0.85</v>
+      </c>
+      <c r="P8" s="36" t="n">
+        <f aca="false">M8*1000/(SQRT(3)*Inputs!$B$6*N8*O8)</f>
+        <v>10.0467831848706</v>
+      </c>
+      <c r="Q8" s="13" t="str">
+        <f aca="false">IF(M8&gt;=Inputs!$B$26,"Star-Delta","DOL")</f>
+        <v>Star-Delta</v>
+      </c>
+      <c r="R8" s="36" t="n">
+        <f aca="false">P8*IF(Q8="DOL",Inputs!$B$24,Inputs!$B$25)</f>
+        <v>20.0935663697412</v>
+      </c>
+      <c r="S8" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="E9" s="33" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" s="33" t="n">
+        <v>30</v>
+      </c>
+      <c r="G9" s="34" t="n">
+        <f aca="false">Inputs!$B$14*Inputs!$B$15*E9*F9/(3600*1000)</f>
+        <v>0.981</v>
+      </c>
+      <c r="H9" s="23" t="n">
+        <f aca="false">Inputs!$B$12</f>
+        <v>0.65</v>
+      </c>
+      <c r="I9" s="34" t="n">
+        <f aca="false">G9/H9</f>
+        <v>1.50923076923077</v>
+      </c>
+      <c r="J9" s="34" t="n">
+        <f aca="false">I9*Inputs!$B$13</f>
+        <v>1.81107692307692</v>
+      </c>
+      <c r="K9" s="34" t="n">
+        <f aca="false">INDEX(Inputs!$F$5:$F$19,COUNTIF(Inputs!$F$5:$F$19,"&lt;"&amp;J9)+1)</f>
+        <v>2.2</v>
+      </c>
+      <c r="L9" s="33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M9" s="34" t="n">
+        <f aca="false">IF(Inputs!$B$27="Calculated",K9,L9)</f>
+        <v>5.5</v>
+      </c>
+      <c r="N9" s="35" t="n">
+        <f aca="false">Inputs!$B$11</f>
+        <v>0.896</v>
+      </c>
+      <c r="O9" s="23" t="n">
+        <f aca="false">Inputs!$B$9</f>
+        <v>0.85</v>
+      </c>
+      <c r="P9" s="36" t="n">
+        <f aca="false">M9*1000/(SQRT(3)*Inputs!$B$6*N9*O9)</f>
+        <v>10.0467831848706</v>
+      </c>
+      <c r="Q9" s="13" t="str">
+        <f aca="false">IF(M9&gt;=Inputs!$B$26,"Star-Delta","DOL")</f>
+        <v>Star-Delta</v>
+      </c>
+      <c r="R9" s="36" t="n">
+        <f aca="false">P9*IF(Q9="DOL",Inputs!$B$24,Inputs!$B$25)</f>
+        <v>20.0935663697412</v>
+      </c>
+      <c r="S9" s="7" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C11" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="M11" s="37" t="n">
+        <f aca="false">SUM(M5:M9)</f>
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C12" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="M12" s="37" t="n">
+        <f aca="false">SUMIF(D5:D9,"Duty",M5:M9)</f>
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C13" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="M13" s="37" t="n">
+        <f aca="false">MAX(M5:M9)</f>
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="38" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="39" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="39" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="39" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="39" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="39" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="39" t="s">
+        <v>216</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1:Z24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="10" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="23" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="10" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="23" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="40"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>161</v>
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="U4" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="V4" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="W4" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="X4" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y4" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="Z4" s="3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="D5" s="8" t="n">
+      <c r="A4" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="V4" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="X4" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="Y4" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="Z4" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="D5" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="23" t="n">
         <f aca="false">'Pump Sizing'!M5</f>
         <v>5.5</v>
       </c>
-      <c r="G5" s="18" t="n">
+      <c r="G5" s="34" t="n">
         <f aca="false">E5*F5</f>
         <v>5.5</v>
       </c>
-      <c r="H5" s="19" t="n">
+      <c r="H5" s="23" t="n">
         <f aca="false">IF(C5="Motor",Inputs!$B$9,Inputs!$B$10)</f>
         <v>0.85</v>
       </c>
-      <c r="I5" s="20" t="n">
+      <c r="I5" s="35" t="n">
         <f aca="false">IF(C5="Motor",Inputs!$B$11,1)</f>
         <v>0.896</v>
       </c>
-      <c r="J5" s="21" t="n">
+      <c r="J5" s="36" t="n">
         <f aca="false">IF(D5=3,G5*1000/(SQRT(3)*Inputs!$B$6*H5*I5),G5*1000/(Inputs!$B$8*H5*I5))</f>
         <v>10.0467831848706</v>
       </c>
-      <c r="K5" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="L5" s="26" t="n">
+      <c r="K5" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="L5" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="M5" s="18" t="n">
+      <c r="M5" s="34" t="n">
         <f aca="false">IF(K5="Y",G5*L5/I5,0)</f>
         <v>6.13839285714286</v>
       </c>
-      <c r="N5" s="18" t="n">
+      <c r="N5" s="34" t="n">
         <f aca="false">M5/H5</f>
         <v>7.22163865546218</v>
       </c>
-      <c r="O5" s="19" t="n">
+      <c r="O5" s="23" t="n">
         <f aca="false">IF(C5="Motor",Inputs!$B$17,Inputs!$B$18)</f>
         <v>2</v>
       </c>
-      <c r="P5" s="21" t="n">
+      <c r="P5" s="36" t="n">
         <f aca="false">J5*O5</f>
         <v>20.0935663697412</v>
       </c>
-      <c r="Q5" s="27" t="n">
+      <c r="Q5" s="41" t="n">
         <f aca="false">INDEX(Inputs!$H$5:$H$22,COUNTIF(Inputs!$H$5:$H$22,"&lt;"&amp;P5)+1)</f>
         <v>25</v>
       </c>
-      <c r="R5" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="S5" s="9" t="str">
+      <c r="R5" s="32" t="s">
+        <v>244</v>
+      </c>
+      <c r="S5" s="13" t="str">
         <f aca="false">IF(C5&lt;&gt;"Motor","-",IF(F5&gt;=Inputs!$B$26,"Star-Delta","DOL"))</f>
         <v>Star-Delta</v>
       </c>
-      <c r="T5" s="28" t="n">
+      <c r="T5" s="42" t="n">
         <v>30</v>
       </c>
-      <c r="U5" s="21" t="n">
+      <c r="U5" s="36" t="n">
         <f aca="false">Q5/Inputs!$B$19</f>
         <v>28.735632183908</v>
       </c>
-      <c r="V5" s="21" t="n">
+      <c r="V5" s="36" t="n">
         <f aca="false">INDEX(Inputs!$J$5:$J$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U5)+1)</f>
         <v>2.5</v>
       </c>
-      <c r="W5" s="27" t="n">
+      <c r="W5" s="41" t="n">
         <f aca="false">INDEX(Inputs!$K$5:$K$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U5)+1)</f>
         <v>30</v>
       </c>
-      <c r="X5" s="18" t="n">
+      <c r="X5" s="34" t="n">
         <f aca="false">INDEX(Inputs!$L$5:$L$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U5)+1)*J5*T5/1000</f>
         <v>5.42526291983013</v>
       </c>
-      <c r="Y5" s="29" t="n">
+      <c r="Y5" s="43" t="n">
         <f aca="false">X5/IF(D5=3,Inputs!$B$6,Inputs!$B$8)</f>
         <v>0.0130729226983858</v>
       </c>
-      <c r="Z5" s="9" t="str">
+      <c r="Z5" s="13" t="str">
         <f aca="false">IF(Y5&lt;=IF(C5="Motor",Inputs!$B$20,Inputs!$B$21),"OK","EXCEEDS LIMIT - upsize cable")&amp;" - "&amp;"Star-Delta per drawing"</f>
         <v>OK - Star-Delta per drawing</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="D6" s="8" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="D6" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="23" t="n">
         <f aca="false">'Pump Sizing'!M6</f>
         <v>5.5</v>
       </c>
-      <c r="G6" s="18" t="n">
+      <c r="G6" s="34" t="n">
         <f aca="false">E6*F6</f>
         <v>5.5</v>
       </c>
-      <c r="H6" s="19" t="n">
+      <c r="H6" s="23" t="n">
         <f aca="false">IF(C6="Motor",Inputs!$B$9,Inputs!$B$10)</f>
         <v>0.85</v>
       </c>
-      <c r="I6" s="20" t="n">
+      <c r="I6" s="35" t="n">
         <f aca="false">IF(C6="Motor",Inputs!$B$11,1)</f>
         <v>0.896</v>
       </c>
-      <c r="J6" s="21" t="n">
+      <c r="J6" s="36" t="n">
         <f aca="false">IF(D6=3,G6*1000/(SQRT(3)*Inputs!$B$6*H6*I6),G6*1000/(Inputs!$B$8*H6*I6))</f>
         <v>10.0467831848706</v>
       </c>
-      <c r="K6" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="L6" s="26" t="n">
+      <c r="K6" s="32" t="s">
+        <v>246</v>
+      </c>
+      <c r="L6" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="M6" s="18" t="n">
+      <c r="M6" s="34" t="n">
         <f aca="false">IF(K6="Y",G6*L6/I6,0)</f>
         <v>0</v>
       </c>
-      <c r="N6" s="18" t="n">
+      <c r="N6" s="34" t="n">
         <f aca="false">M6/H6</f>
         <v>0</v>
       </c>
-      <c r="O6" s="19" t="n">
+      <c r="O6" s="23" t="n">
         <f aca="false">IF(C6="Motor",Inputs!$B$17,Inputs!$B$18)</f>
         <v>2</v>
       </c>
-      <c r="P6" s="21" t="n">
+      <c r="P6" s="36" t="n">
         <f aca="false">J6*O6</f>
         <v>20.0935663697412</v>
       </c>
-      <c r="Q6" s="27" t="n">
+      <c r="Q6" s="41" t="n">
         <f aca="false">INDEX(Inputs!$H$5:$H$22,COUNTIF(Inputs!$H$5:$H$22,"&lt;"&amp;P6)+1)</f>
         <v>25</v>
       </c>
-      <c r="R6" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="S6" s="9" t="str">
+      <c r="R6" s="32" t="s">
+        <v>244</v>
+      </c>
+      <c r="S6" s="13" t="str">
         <f aca="false">IF(C6&lt;&gt;"Motor","-",IF(F6&gt;=Inputs!$B$26,"Star-Delta","DOL"))</f>
         <v>Star-Delta</v>
       </c>
-      <c r="T6" s="28" t="n">
+      <c r="T6" s="42" t="n">
         <v>30</v>
       </c>
-      <c r="U6" s="21" t="n">
+      <c r="U6" s="36" t="n">
         <f aca="false">Q6/Inputs!$B$19</f>
         <v>28.735632183908</v>
       </c>
-      <c r="V6" s="21" t="n">
+      <c r="V6" s="36" t="n">
         <f aca="false">INDEX(Inputs!$J$5:$J$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U6)+1)</f>
         <v>2.5</v>
       </c>
-      <c r="W6" s="27" t="n">
+      <c r="W6" s="41" t="n">
         <f aca="false">INDEX(Inputs!$K$5:$K$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U6)+1)</f>
         <v>30</v>
       </c>
-      <c r="X6" s="18" t="n">
+      <c r="X6" s="34" t="n">
         <f aca="false">INDEX(Inputs!$L$5:$L$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U6)+1)*J6*T6/1000</f>
         <v>5.42526291983013</v>
       </c>
-      <c r="Y6" s="29" t="n">
+      <c r="Y6" s="43" t="n">
         <f aca="false">X6/IF(D6=3,Inputs!$B$6,Inputs!$B$8)</f>
         <v>0.0130729226983858</v>
       </c>
-      <c r="Z6" s="9" t="str">
+      <c r="Z6" s="13" t="str">
         <f aca="false">IF(Y6&lt;=IF(C6="Motor",Inputs!$B$20,Inputs!$B$21),"OK","EXCEEDS LIMIT - upsize cable")&amp;" - "&amp;"Standby - interlocked with MCC-1"</f>
         <v>OK - Standby - interlocked with MCC-1</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="D7" s="8" t="n">
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="D7" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="23" t="n">
         <f aca="false">'Pump Sizing'!M7</f>
         <v>5.5</v>
       </c>
-      <c r="G7" s="18" t="n">
+      <c r="G7" s="34" t="n">
         <f aca="false">E7*F7</f>
         <v>5.5</v>
       </c>
-      <c r="H7" s="19" t="n">
+      <c r="H7" s="23" t="n">
         <f aca="false">IF(C7="Motor",Inputs!$B$9,Inputs!$B$10)</f>
         <v>0.85</v>
       </c>
-      <c r="I7" s="20" t="n">
+      <c r="I7" s="35" t="n">
         <f aca="false">IF(C7="Motor",Inputs!$B$11,1)</f>
         <v>0.896</v>
       </c>
-      <c r="J7" s="21" t="n">
+      <c r="J7" s="36" t="n">
         <f aca="false">IF(D7=3,G7*1000/(SQRT(3)*Inputs!$B$6*H7*I7),G7*1000/(Inputs!$B$8*H7*I7))</f>
         <v>10.0467831848706</v>
       </c>
-      <c r="K7" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="L7" s="26" t="n">
+      <c r="K7" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="L7" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="M7" s="18" t="n">
+      <c r="M7" s="34" t="n">
         <f aca="false">IF(K7="Y",G7*L7/I7,0)</f>
         <v>6.13839285714286</v>
       </c>
-      <c r="N7" s="18" t="n">
+      <c r="N7" s="34" t="n">
         <f aca="false">M7/H7</f>
         <v>7.22163865546218</v>
       </c>
-      <c r="O7" s="19" t="n">
+      <c r="O7" s="23" t="n">
         <f aca="false">IF(C7="Motor",Inputs!$B$17,Inputs!$B$18)</f>
         <v>2</v>
       </c>
-      <c r="P7" s="21" t="n">
+      <c r="P7" s="36" t="n">
         <f aca="false">J7*O7</f>
         <v>20.0935663697412</v>
       </c>
-      <c r="Q7" s="27" t="n">
+      <c r="Q7" s="41" t="n">
         <f aca="false">INDEX(Inputs!$H$5:$H$22,COUNTIF(Inputs!$H$5:$H$22,"&lt;"&amp;P7)+1)</f>
         <v>25</v>
       </c>
-      <c r="R7" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="S7" s="9" t="str">
+      <c r="R7" s="32" t="s">
+        <v>244</v>
+      </c>
+      <c r="S7" s="13" t="str">
         <f aca="false">IF(C7&lt;&gt;"Motor","-",IF(F7&gt;=Inputs!$B$26,"Star-Delta","DOL"))</f>
         <v>Star-Delta</v>
       </c>
-      <c r="T7" s="28" t="n">
+      <c r="T7" s="42" t="n">
         <v>30</v>
       </c>
-      <c r="U7" s="21" t="n">
+      <c r="U7" s="36" t="n">
         <f aca="false">Q7/Inputs!$B$19</f>
         <v>28.735632183908</v>
       </c>
-      <c r="V7" s="21" t="n">
+      <c r="V7" s="36" t="n">
         <f aca="false">INDEX(Inputs!$J$5:$J$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U7)+1)</f>
         <v>2.5</v>
       </c>
-      <c r="W7" s="27" t="n">
+      <c r="W7" s="41" t="n">
         <f aca="false">INDEX(Inputs!$K$5:$K$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U7)+1)</f>
         <v>30</v>
       </c>
-      <c r="X7" s="18" t="n">
+      <c r="X7" s="34" t="n">
         <f aca="false">INDEX(Inputs!$L$5:$L$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U7)+1)*J7*T7/1000</f>
         <v>5.42526291983013</v>
       </c>
-      <c r="Y7" s="29" t="n">
+      <c r="Y7" s="43" t="n">
         <f aca="false">X7/IF(D7=3,Inputs!$B$6,Inputs!$B$8)</f>
         <v>0.0130729226983858</v>
       </c>
-      <c r="Z7" s="9" t="str">
+      <c r="Z7" s="13" t="str">
         <f aca="false">IF(Y7&lt;=IF(C7="Motor",Inputs!$B$20,Inputs!$B$21),"OK","EXCEEDS LIMIT - upsize cable")&amp;" - "&amp;"Counted as running: backwash may overlap with raw water pumping (conservative)"</f>
         <v>OK - Counted as running: backwash may overlap with raw water pumping (conservative)</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="D8" s="8" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="D8" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="23" t="n">
         <f aca="false">'Pump Sizing'!M8</f>
         <v>5.5</v>
       </c>
-      <c r="G8" s="18" t="n">
+      <c r="G8" s="34" t="n">
         <f aca="false">E8*F8</f>
         <v>5.5</v>
       </c>
-      <c r="H8" s="19" t="n">
+      <c r="H8" s="23" t="n">
         <f aca="false">IF(C8="Motor",Inputs!$B$9,Inputs!$B$10)</f>
         <v>0.85</v>
       </c>
-      <c r="I8" s="20" t="n">
+      <c r="I8" s="35" t="n">
         <f aca="false">IF(C8="Motor",Inputs!$B$11,1)</f>
         <v>0.896</v>
       </c>
-      <c r="J8" s="21" t="n">
+      <c r="J8" s="36" t="n">
         <f aca="false">IF(D8=3,G8*1000/(SQRT(3)*Inputs!$B$6*H8*I8),G8*1000/(Inputs!$B$8*H8*I8))</f>
         <v>10.0467831848706</v>
       </c>
-      <c r="K8" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="L8" s="26" t="n">
+      <c r="K8" s="32" t="s">
+        <v>246</v>
+      </c>
+      <c r="L8" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="M8" s="18" t="n">
+      <c r="M8" s="34" t="n">
         <f aca="false">IF(K8="Y",G8*L8/I8,0)</f>
         <v>0</v>
       </c>
-      <c r="N8" s="18" t="n">
+      <c r="N8" s="34" t="n">
         <f aca="false">M8/H8</f>
         <v>0</v>
       </c>
-      <c r="O8" s="19" t="n">
+      <c r="O8" s="23" t="n">
         <f aca="false">IF(C8="Motor",Inputs!$B$17,Inputs!$B$18)</f>
         <v>2</v>
       </c>
-      <c r="P8" s="21" t="n">
+      <c r="P8" s="36" t="n">
         <f aca="false">J8*O8</f>
         <v>20.0935663697412</v>
       </c>
-      <c r="Q8" s="27" t="n">
+      <c r="Q8" s="41" t="n">
         <f aca="false">INDEX(Inputs!$H$5:$H$22,COUNTIF(Inputs!$H$5:$H$22,"&lt;"&amp;P8)+1)</f>
         <v>25</v>
       </c>
-      <c r="R8" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="S8" s="9" t="str">
+      <c r="R8" s="32" t="s">
+        <v>244</v>
+      </c>
+      <c r="S8" s="13" t="str">
         <f aca="false">IF(C8&lt;&gt;"Motor","-",IF(F8&gt;=Inputs!$B$26,"Star-Delta","DOL"))</f>
         <v>Star-Delta</v>
       </c>
-      <c r="T8" s="28" t="n">
+      <c r="T8" s="42" t="n">
         <v>30</v>
       </c>
-      <c r="U8" s="21" t="n">
+      <c r="U8" s="36" t="n">
         <f aca="false">Q8/Inputs!$B$19</f>
         <v>28.735632183908</v>
       </c>
-      <c r="V8" s="21" t="n">
+      <c r="V8" s="36" t="n">
         <f aca="false">INDEX(Inputs!$J$5:$J$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U8)+1)</f>
         <v>2.5</v>
       </c>
-      <c r="W8" s="27" t="n">
+      <c r="W8" s="41" t="n">
         <f aca="false">INDEX(Inputs!$K$5:$K$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U8)+1)</f>
         <v>30</v>
       </c>
-      <c r="X8" s="18" t="n">
+      <c r="X8" s="34" t="n">
         <f aca="false">INDEX(Inputs!$L$5:$L$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U8)+1)*J8*T8/1000</f>
         <v>5.42526291983013</v>
       </c>
-      <c r="Y8" s="29" t="n">
+      <c r="Y8" s="43" t="n">
         <f aca="false">X8/IF(D8=3,Inputs!$B$6,Inputs!$B$8)</f>
         <v>0.0130729226983858</v>
       </c>
-      <c r="Z8" s="9" t="str">
+      <c r="Z8" s="13" t="str">
         <f aca="false">IF(Y8&lt;=IF(C8="Motor",Inputs!$B$20,Inputs!$B$21),"OK","EXCEEDS LIMIT - upsize cable")&amp;" - "&amp;"Standby - interlocked with MCC-3"</f>
         <v>OK - Standby - interlocked with MCC-3</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="D9" s="8" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="D9" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E9" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="23" t="n">
         <f aca="false">'Pump Sizing'!M9</f>
         <v>5.5</v>
       </c>
-      <c r="G9" s="18" t="n">
+      <c r="G9" s="34" t="n">
         <f aca="false">E9*F9</f>
         <v>5.5</v>
       </c>
-      <c r="H9" s="19" t="n">
+      <c r="H9" s="23" t="n">
         <f aca="false">IF(C9="Motor",Inputs!$B$9,Inputs!$B$10)</f>
         <v>0.85</v>
       </c>
-      <c r="I9" s="20" t="n">
+      <c r="I9" s="35" t="n">
         <f aca="false">IF(C9="Motor",Inputs!$B$11,1)</f>
         <v>0.896</v>
       </c>
-      <c r="J9" s="21" t="n">
+      <c r="J9" s="36" t="n">
         <f aca="false">IF(D9=3,G9*1000/(SQRT(3)*Inputs!$B$6*H9*I9),G9*1000/(Inputs!$B$8*H9*I9))</f>
         <v>10.0467831848706</v>
       </c>
-      <c r="K9" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="L9" s="26" t="n">
+      <c r="K9" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="L9" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="M9" s="18" t="n">
+      <c r="M9" s="34" t="n">
         <f aca="false">IF(K9="Y",G9*L9/I9,0)</f>
         <v>6.13839285714286</v>
       </c>
-      <c r="N9" s="18" t="n">
+      <c r="N9" s="34" t="n">
         <f aca="false">M9/H9</f>
         <v>7.22163865546218</v>
       </c>
-      <c r="O9" s="19" t="n">
+      <c r="O9" s="23" t="n">
         <f aca="false">IF(C9="Motor",Inputs!$B$17,Inputs!$B$18)</f>
         <v>2</v>
       </c>
-      <c r="P9" s="21" t="n">
+      <c r="P9" s="36" t="n">
         <f aca="false">J9*O9</f>
         <v>20.0935663697412</v>
       </c>
-      <c r="Q9" s="27" t="n">
+      <c r="Q9" s="41" t="n">
         <f aca="false">INDEX(Inputs!$H$5:$H$22,COUNTIF(Inputs!$H$5:$H$22,"&lt;"&amp;P9)+1)</f>
         <v>25</v>
       </c>
-      <c r="R9" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="S9" s="9" t="str">
+      <c r="R9" s="32" t="s">
+        <v>244</v>
+      </c>
+      <c r="S9" s="13" t="str">
         <f aca="false">IF(C9&lt;&gt;"Motor","-",IF(F9&gt;=Inputs!$B$26,"Star-Delta","DOL"))</f>
         <v>Star-Delta</v>
       </c>
-      <c r="T9" s="28" t="n">
+      <c r="T9" s="42" t="n">
         <v>40</v>
       </c>
-      <c r="U9" s="21" t="n">
+      <c r="U9" s="36" t="n">
         <f aca="false">Q9/Inputs!$B$19</f>
         <v>28.735632183908</v>
       </c>
-      <c r="V9" s="21" t="n">
+      <c r="V9" s="36" t="n">
         <f aca="false">INDEX(Inputs!$J$5:$J$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U9)+1)</f>
         <v>2.5</v>
       </c>
-      <c r="W9" s="27" t="n">
+      <c r="W9" s="41" t="n">
         <f aca="false">INDEX(Inputs!$K$5:$K$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U9)+1)</f>
         <v>30</v>
       </c>
-      <c r="X9" s="18" t="n">
+      <c r="X9" s="34" t="n">
         <f aca="false">INDEX(Inputs!$L$5:$L$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U9)+1)*J9*T9/1000</f>
         <v>7.23368389310683</v>
       </c>
-      <c r="Y9" s="29" t="n">
+      <c r="Y9" s="43" t="n">
         <f aca="false">X9/IF(D9=3,Inputs!$B$6,Inputs!$B$8)</f>
         <v>0.0174305635978478</v>
       </c>
-      <c r="Z9" s="9" t="str">
+      <c r="Z9" s="13" t="str">
         <f aca="false">IF(Y9&lt;=IF(C9="Motor",Inputs!$B$20,Inputs!$B$21),"OK","EXCEEDS LIMIT - upsize cable")&amp;" - "&amp;"Longest run, to elevated tank side of shelter"</f>
         <v>OK - Longest run, to elevated tank side of shelter</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="D10" s="8" t="n">
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>251</v>
+      </c>
+      <c r="D10" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="E10" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="30" t="n">
+      <c r="F10" s="44" t="n">
         <v>1.5</v>
       </c>
-      <c r="G10" s="18" t="n">
+      <c r="G10" s="34" t="n">
         <f aca="false">E10*F10</f>
         <v>1.5</v>
       </c>
-      <c r="H10" s="19" t="n">
+      <c r="H10" s="23" t="n">
         <f aca="false">IF(C10="Motor",Inputs!$B$9,Inputs!$B$10)</f>
         <v>0.9</v>
       </c>
-      <c r="I10" s="20" t="n">
+      <c r="I10" s="35" t="n">
         <f aca="false">IF(C10="Motor",Inputs!$B$11,1)</f>
         <v>1</v>
       </c>
-      <c r="J10" s="21" t="n">
+      <c r="J10" s="36" t="n">
         <f aca="false">IF(D10=3,G10*1000/(SQRT(3)*Inputs!$B$6*H10*I10),G10*1000/(Inputs!$B$8*H10*I10))</f>
         <v>6.94444444444445</v>
       </c>
-      <c r="K10" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="L10" s="19" t="n">
+      <c r="K10" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="L10" s="23" t="n">
         <f aca="false">Inputs!$B$22</f>
         <v>0.8</v>
       </c>
-      <c r="M10" s="18" t="n">
+      <c r="M10" s="34" t="n">
         <f aca="false">IF(K10="Y",G10*L10/I10,0)</f>
         <v>1.2</v>
       </c>
-      <c r="N10" s="18" t="n">
+      <c r="N10" s="34" t="n">
         <f aca="false">M10/H10</f>
         <v>1.33333333333333</v>
       </c>
-      <c r="O10" s="19" t="n">
+      <c r="O10" s="23" t="n">
         <f aca="false">IF(C10="Motor",Inputs!$B$17,Inputs!$B$18)</f>
         <v>1.25</v>
       </c>
-      <c r="P10" s="21" t="n">
+      <c r="P10" s="36" t="n">
         <f aca="false">J10*O10</f>
         <v>8.68055555555556</v>
       </c>
-      <c r="Q10" s="27" t="n">
+      <c r="Q10" s="41" t="n">
         <f aca="false">INDEX(Inputs!$H$5:$H$22,COUNTIF(Inputs!$H$5:$H$22,"&lt;"&amp;P10)+1)</f>
         <v>10</v>
       </c>
-      <c r="R10" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="S10" s="9" t="str">
+      <c r="R10" s="32" t="s">
+        <v>252</v>
+      </c>
+      <c r="S10" s="13" t="str">
         <f aca="false">IF(C10&lt;&gt;"Motor","-",IF(F10&gt;=Inputs!$B$26,"Star-Delta","DOL"))</f>
         <v>-</v>
       </c>
-      <c r="T10" s="28" t="n">
+      <c r="T10" s="42" t="n">
         <v>25</v>
       </c>
-      <c r="U10" s="21" t="n">
+      <c r="U10" s="36" t="n">
         <f aca="false">Q10/Inputs!$B$19</f>
         <v>11.4942528735632</v>
       </c>
-      <c r="V10" s="21" t="n">
+      <c r="V10" s="36" t="n">
         <f aca="false">INDEX(Inputs!$J$5:$J$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U10)+1)</f>
         <v>1.5</v>
       </c>
-      <c r="W10" s="27" t="n">
+      <c r="W10" s="41" t="n">
         <f aca="false">INDEX(Inputs!$K$5:$K$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U10)+1)</f>
         <v>22</v>
       </c>
-      <c r="X10" s="18" t="n">
+      <c r="X10" s="34" t="n">
         <f aca="false">INDEX(Inputs!$L$5:$L$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U10)+1)*J10*T10/1000</f>
         <v>5.03472222222222</v>
       </c>
-      <c r="Y10" s="29" t="n">
+      <c r="Y10" s="43" t="n">
         <f aca="false">X10/IF(D10=3,Inputs!$B$6,Inputs!$B$8)</f>
         <v>0.0209780092592593</v>
       </c>
-      <c r="Z10" s="9" t="str">
+      <c r="Z10" s="13" t="str">
         <f aca="false">IF(Y10&lt;=IF(C10="Motor",Inputs!$B$20,Inputs!$B$21),"OK","EXCEEDS LIMIT - upsize cable")&amp;" - "&amp;"Assumed 1.5 kW LED lighting (approx. 11 W/m2 x 132 m2). Drawing: MCB 1P 10A"</f>
         <v>OK - Assumed 1.5 kW LED lighting (approx. 11 W/m2 x 132 m2). Drawing: MCB 1P 10A</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="D11" s="8" t="n">
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="D11" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="E11" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="30" t="n">
+      <c r="F11" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="18" t="n">
+      <c r="G11" s="34" t="n">
         <f aca="false">E11*F11</f>
         <v>2</v>
       </c>
-      <c r="H11" s="19" t="n">
+      <c r="H11" s="23" t="n">
         <f aca="false">IF(C11="Motor",Inputs!$B$9,Inputs!$B$10)</f>
         <v>0.9</v>
       </c>
-      <c r="I11" s="20" t="n">
+      <c r="I11" s="35" t="n">
         <f aca="false">IF(C11="Motor",Inputs!$B$11,1)</f>
         <v>1</v>
       </c>
-      <c r="J11" s="21" t="n">
+      <c r="J11" s="36" t="n">
         <f aca="false">IF(D11=3,G11*1000/(SQRT(3)*Inputs!$B$6*H11*I11),G11*1000/(Inputs!$B$8*H11*I11))</f>
         <v>9.25925925925926</v>
       </c>
-      <c r="K11" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="L11" s="19" t="n">
+      <c r="K11" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="L11" s="23" t="n">
         <f aca="false">Inputs!$B$22</f>
         <v>0.8</v>
       </c>
-      <c r="M11" s="18" t="n">
+      <c r="M11" s="34" t="n">
         <f aca="false">IF(K11="Y",G11*L11/I11,0)</f>
         <v>1.6</v>
       </c>
-      <c r="N11" s="18" t="n">
+      <c r="N11" s="34" t="n">
         <f aca="false">M11/H11</f>
         <v>1.77777777777778</v>
       </c>
-      <c r="O11" s="19" t="n">
+      <c r="O11" s="23" t="n">
         <f aca="false">IF(C11="Motor",Inputs!$B$17,Inputs!$B$18)</f>
         <v>1.25</v>
       </c>
-      <c r="P11" s="21" t="n">
+      <c r="P11" s="36" t="n">
         <f aca="false">J11*O11</f>
         <v>11.5740740740741</v>
       </c>
-      <c r="Q11" s="27" t="n">
+      <c r="Q11" s="41" t="n">
         <f aca="false">INDEX(Inputs!$H$5:$H$22,COUNTIF(Inputs!$H$5:$H$22,"&lt;"&amp;P11)+1)</f>
         <v>16</v>
       </c>
-      <c r="R11" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="S11" s="9" t="str">
+      <c r="R11" s="32" t="s">
+        <v>252</v>
+      </c>
+      <c r="S11" s="13" t="str">
         <f aca="false">IF(C11&lt;&gt;"Motor","-",IF(F11&gt;=Inputs!$B$26,"Star-Delta","DOL"))</f>
         <v>-</v>
       </c>
-      <c r="T11" s="28" t="n">
+      <c r="T11" s="42" t="n">
         <v>25</v>
       </c>
-      <c r="U11" s="21" t="n">
+      <c r="U11" s="36" t="n">
         <f aca="false">Q11/Inputs!$B$19</f>
         <v>18.3908045977012</v>
       </c>
-      <c r="V11" s="21" t="n">
+      <c r="V11" s="36" t="n">
         <f aca="false">INDEX(Inputs!$J$5:$J$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U11)+1)</f>
         <v>1.5</v>
       </c>
-      <c r="W11" s="27" t="n">
+      <c r="W11" s="41" t="n">
         <f aca="false">INDEX(Inputs!$K$5:$K$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U11)+1)</f>
         <v>22</v>
       </c>
-      <c r="X11" s="18" t="n">
+      <c r="X11" s="34" t="n">
         <f aca="false">INDEX(Inputs!$L$5:$L$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U11)+1)*J11*T11/1000</f>
         <v>6.71296296296296</v>
       </c>
-      <c r="Y11" s="29" t="n">
+      <c r="Y11" s="43" t="n">
         <f aca="false">X11/IF(D11=3,Inputs!$B$6,Inputs!$B$8)</f>
         <v>0.0279706790123457</v>
       </c>
-      <c r="Z11" s="9" t="str">
+      <c r="Z11" s="13" t="str">
         <f aca="false">IF(Y11&lt;=IF(C11="Motor",Inputs!$B$20,Inputs!$B$21),"OK","EXCEEDS LIMIT - upsize cable")&amp;" - "&amp;"Assumed 2.0 kW allowance. Drawing: MCB 1P 10A"</f>
         <v>OK - Assumed 2.0 kW allowance. Drawing: MCB 1P 10A</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="D12" s="8" t="n">
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="D12" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="E12" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="F12" s="30" t="n">
+      <c r="F12" s="44" t="n">
         <v>0.12</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="34" t="n">
         <f aca="false">E12*F12</f>
         <v>0.48</v>
       </c>
-      <c r="H12" s="19" t="n">
+      <c r="H12" s="23" t="n">
         <f aca="false">IF(C12="Motor",Inputs!$B$9,Inputs!$B$10)</f>
         <v>0.85</v>
       </c>
-      <c r="I12" s="20" t="n">
+      <c r="I12" s="35" t="n">
         <f aca="false">IF(C12="Motor",Inputs!$B$11,1)</f>
         <v>0.896</v>
       </c>
-      <c r="J12" s="21" t="n">
+      <c r="J12" s="36" t="n">
         <f aca="false">IF(D12=3,G12*1000/(SQRT(3)*Inputs!$B$6*H12*I12),G12*1000/(Inputs!$B$8*H12*I12))</f>
         <v>2.62605042016807</v>
       </c>
-      <c r="K12" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="L12" s="26" t="n">
+      <c r="K12" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="L12" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="M12" s="18" t="n">
+      <c r="M12" s="34" t="n">
         <f aca="false">IF(K12="Y",G12*L12/I12,0)</f>
         <v>0.535714285714286</v>
       </c>
-      <c r="N12" s="18" t="n">
+      <c r="N12" s="34" t="n">
         <f aca="false">M12/H12</f>
         <v>0.630252100840336</v>
       </c>
-      <c r="O12" s="19" t="n">
+      <c r="O12" s="23" t="n">
         <f aca="false">IF(C12="Motor",Inputs!$B$17,Inputs!$B$18)</f>
         <v>2</v>
       </c>
-      <c r="P12" s="21" t="n">
+      <c r="P12" s="36" t="n">
         <f aca="false">J12*O12</f>
         <v>5.25210084033613</v>
       </c>
-      <c r="Q12" s="27" t="n">
+      <c r="Q12" s="41" t="n">
         <f aca="false">INDEX(Inputs!$H$5:$H$22,COUNTIF(Inputs!$H$5:$H$22,"&lt;"&amp;P12)+1)</f>
         <v>6</v>
       </c>
-      <c r="R12" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="S12" s="9" t="str">
+      <c r="R12" s="32" t="s">
+        <v>252</v>
+      </c>
+      <c r="S12" s="13" t="str">
         <f aca="false">IF(C12&lt;&gt;"Motor","-",IF(F12&gt;=Inputs!$B$26,"Star-Delta","DOL"))</f>
         <v>DOL</v>
       </c>
-      <c r="T12" s="28" t="n">
+      <c r="T12" s="42" t="n">
         <v>20</v>
       </c>
-      <c r="U12" s="21" t="n">
+      <c r="U12" s="36" t="n">
         <f aca="false">Q12/Inputs!$B$19</f>
         <v>6.89655172413793</v>
       </c>
-      <c r="V12" s="21" t="n">
+      <c r="V12" s="36" t="n">
         <f aca="false">INDEX(Inputs!$J$5:$J$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U12)+1)</f>
         <v>1.5</v>
       </c>
-      <c r="W12" s="27" t="n">
+      <c r="W12" s="41" t="n">
         <f aca="false">INDEX(Inputs!$K$5:$K$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U12)+1)</f>
         <v>22</v>
       </c>
-      <c r="X12" s="18" t="n">
+      <c r="X12" s="34" t="n">
         <f aca="false">INDEX(Inputs!$L$5:$L$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U12)+1)*J12*T12/1000</f>
         <v>1.52310924369748</v>
       </c>
-      <c r="Y12" s="29" t="n">
+      <c r="Y12" s="43" t="n">
         <f aca="false">X12/IF(D12=3,Inputs!$B$6,Inputs!$B$8)</f>
         <v>0.00634628851540616</v>
       </c>
-      <c r="Z12" s="9" t="str">
+      <c r="Z12" s="13" t="str">
         <f aca="false">IF(Y12&lt;=IF(C12="Motor",Inputs!$B$20,Inputs!$B$21),"OK","EXCEEDS LIMIT - upsize cable")&amp;" - "&amp;"Assumed 0.12 kW each diaphragm dosing pump. Drawing: MCB 1P 6A"</f>
         <v>OK - Assumed 0.12 kW each diaphragm dosing pump. Drawing: MCB 1P 6A</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="D13" s="8" t="n">
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="D13" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E13" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="F13" s="30" t="n">
+      <c r="F13" s="44" t="n">
         <v>0.37</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="G13" s="34" t="n">
         <f aca="false">E13*F13</f>
         <v>1.48</v>
       </c>
-      <c r="H13" s="19" t="n">
+      <c r="H13" s="23" t="n">
         <f aca="false">IF(C13="Motor",Inputs!$B$9,Inputs!$B$10)</f>
         <v>0.85</v>
       </c>
-      <c r="I13" s="20" t="n">
+      <c r="I13" s="35" t="n">
         <f aca="false">IF(C13="Motor",Inputs!$B$11,1)</f>
         <v>0.896</v>
       </c>
-      <c r="J13" s="21" t="n">
+      <c r="J13" s="36" t="n">
         <f aca="false">IF(D13=3,G13*1000/(SQRT(3)*Inputs!$B$6*H13*I13),G13*1000/(Inputs!$B$8*H13*I13))</f>
         <v>8.09698879551821</v>
       </c>
-      <c r="K13" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="L13" s="26" t="n">
+      <c r="K13" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="L13" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="M13" s="18" t="n">
+      <c r="M13" s="34" t="n">
         <f aca="false">IF(K13="Y",G13*L13/I13,0)</f>
         <v>1.65178571428571</v>
       </c>
-      <c r="N13" s="18" t="n">
+      <c r="N13" s="34" t="n">
         <f aca="false">M13/H13</f>
         <v>1.94327731092437</v>
       </c>
-      <c r="O13" s="19" t="n">
+      <c r="O13" s="23" t="n">
         <f aca="false">IF(C13="Motor",Inputs!$B$17,Inputs!$B$18)</f>
         <v>2</v>
       </c>
-      <c r="P13" s="21" t="n">
+      <c r="P13" s="36" t="n">
         <f aca="false">J13*O13</f>
         <v>16.1939775910364</v>
       </c>
-      <c r="Q13" s="27" t="n">
+      <c r="Q13" s="41" t="n">
         <f aca="false">INDEX(Inputs!$H$5:$H$22,COUNTIF(Inputs!$H$5:$H$22,"&lt;"&amp;P13)+1)</f>
         <v>20</v>
       </c>
-      <c r="R13" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="S13" s="9" t="str">
+      <c r="R13" s="32" t="s">
+        <v>252</v>
+      </c>
+      <c r="S13" s="13" t="str">
         <f aca="false">IF(C13&lt;&gt;"Motor","-",IF(F13&gt;=Inputs!$B$26,"Star-Delta","DOL"))</f>
         <v>DOL</v>
       </c>
-      <c r="T13" s="28" t="n">
+      <c r="T13" s="42" t="n">
         <v>20</v>
       </c>
-      <c r="U13" s="21" t="n">
+      <c r="U13" s="36" t="n">
         <f aca="false">Q13/Inputs!$B$19</f>
         <v>22.9885057471264</v>
       </c>
-      <c r="V13" s="21" t="n">
+      <c r="V13" s="36" t="n">
         <f aca="false">INDEX(Inputs!$J$5:$J$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U13)+1)</f>
         <v>2.5</v>
       </c>
-      <c r="W13" s="27" t="n">
+      <c r="W13" s="41" t="n">
         <f aca="false">INDEX(Inputs!$K$5:$K$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U13)+1)</f>
         <v>30</v>
       </c>
-      <c r="X13" s="18" t="n">
+      <c r="X13" s="34" t="n">
         <f aca="false">INDEX(Inputs!$L$5:$L$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U13)+1)*J13*T13/1000</f>
         <v>2.91491596638655</v>
       </c>
-      <c r="Y13" s="29" t="n">
+      <c r="Y13" s="43" t="n">
         <f aca="false">X13/IF(D13=3,Inputs!$B$6,Inputs!$B$8)</f>
         <v>0.0121454831932773</v>
       </c>
-      <c r="Z13" s="9" t="str">
+      <c r="Z13" s="13" t="str">
         <f aca="false">IF(Y13&lt;=IF(C13="Motor",Inputs!$B$20,Inputs!$B$21),"OK","EXCEEDS LIMIT - upsize cable")&amp;" - "&amp;"Assumed 0.37 kW each. Drawing: MCB 1P 6A"</f>
         <v>OK - Assumed 0.37 kW each. Drawing: MCB 1P 6A</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="D14" s="8" t="n">
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="D14" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E14" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="30" t="n">
+      <c r="F14" s="44" t="n">
         <v>0.5</v>
       </c>
-      <c r="G14" s="18" t="n">
+      <c r="G14" s="34" t="n">
         <f aca="false">E14*F14</f>
         <v>0.5</v>
       </c>
-      <c r="H14" s="19" t="n">
+      <c r="H14" s="23" t="n">
         <f aca="false">IF(C14="Motor",Inputs!$B$9,Inputs!$B$10)</f>
         <v>0.9</v>
       </c>
-      <c r="I14" s="20" t="n">
+      <c r="I14" s="35" t="n">
         <f aca="false">IF(C14="Motor",Inputs!$B$11,1)</f>
         <v>1</v>
       </c>
-      <c r="J14" s="21" t="n">
+      <c r="J14" s="36" t="n">
         <f aca="false">IF(D14=3,G14*1000/(SQRT(3)*Inputs!$B$6*H14*I14),G14*1000/(Inputs!$B$8*H14*I14))</f>
         <v>2.31481481481482</v>
       </c>
-      <c r="K14" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="L14" s="26" t="n">
+      <c r="K14" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="L14" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="M14" s="18" t="n">
+      <c r="M14" s="34" t="n">
         <f aca="false">IF(K14="Y",G14*L14/I14,0)</f>
         <v>0.5</v>
       </c>
-      <c r="N14" s="18" t="n">
+      <c r="N14" s="34" t="n">
         <f aca="false">M14/H14</f>
         <v>0.555555555555556</v>
       </c>
-      <c r="O14" s="19" t="n">
+      <c r="O14" s="23" t="n">
         <f aca="false">IF(C14="Motor",Inputs!$B$17,Inputs!$B$18)</f>
         <v>1.25</v>
       </c>
-      <c r="P14" s="21" t="n">
+      <c r="P14" s="36" t="n">
         <f aca="false">J14*O14</f>
         <v>2.89351851851852</v>
       </c>
-      <c r="Q14" s="27" t="n">
+      <c r="Q14" s="41" t="n">
         <f aca="false">INDEX(Inputs!$H$5:$H$22,COUNTIF(Inputs!$H$5:$H$22,"&lt;"&amp;P14)+1)</f>
         <v>6</v>
       </c>
-      <c r="R14" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="S14" s="9" t="str">
+      <c r="R14" s="32" t="s">
+        <v>252</v>
+      </c>
+      <c r="S14" s="13" t="str">
         <f aca="false">IF(C14&lt;&gt;"Motor","-",IF(F14&gt;=Inputs!$B$26,"Star-Delta","DOL"))</f>
         <v>-</v>
       </c>
-      <c r="T14" s="28" t="n">
+      <c r="T14" s="42" t="n">
         <v>10</v>
       </c>
-      <c r="U14" s="21" t="n">
+      <c r="U14" s="36" t="n">
         <f aca="false">Q14/Inputs!$B$19</f>
         <v>6.89655172413793</v>
       </c>
-      <c r="V14" s="21" t="n">
+      <c r="V14" s="36" t="n">
         <f aca="false">INDEX(Inputs!$J$5:$J$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U14)+1)</f>
         <v>1.5</v>
       </c>
-      <c r="W14" s="27" t="n">
+      <c r="W14" s="41" t="n">
         <f aca="false">INDEX(Inputs!$K$5:$K$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U14)+1)</f>
         <v>22</v>
       </c>
-      <c r="X14" s="18" t="n">
+      <c r="X14" s="34" t="n">
         <f aca="false">INDEX(Inputs!$L$5:$L$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U14)+1)*J14*T14/1000</f>
         <v>0.671296296296296</v>
       </c>
-      <c r="Y14" s="29" t="n">
+      <c r="Y14" s="43" t="n">
         <f aca="false">X14/IF(D14=3,Inputs!$B$6,Inputs!$B$8)</f>
         <v>0.00279706790123457</v>
       </c>
-      <c r="Z14" s="9" t="str">
+      <c r="Z14" s="13" t="str">
         <f aca="false">IF(Y14&lt;=IF(C14="Motor",Inputs!$B$20,Inputs!$B$21),"OK","EXCEEDS LIMIT - upsize cable")&amp;" - "&amp;"Not shown on drawing - added as assumed load for auto operation"</f>
         <v>OK - Not shown on drawing - added as assumed load for auto operation</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="D15" s="8" t="n">
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="D15" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="8" t="n">
+      <c r="E15" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="30" t="n">
+      <c r="F15" s="44" t="n">
         <v>0.5</v>
       </c>
-      <c r="G15" s="18" t="n">
+      <c r="G15" s="34" t="n">
         <f aca="false">E15*F15</f>
         <v>0.5</v>
       </c>
-      <c r="H15" s="19" t="n">
+      <c r="H15" s="23" t="n">
         <f aca="false">IF(C15="Motor",Inputs!$B$9,Inputs!$B$10)</f>
         <v>0.9</v>
       </c>
-      <c r="I15" s="20" t="n">
+      <c r="I15" s="35" t="n">
         <f aca="false">IF(C15="Motor",Inputs!$B$11,1)</f>
         <v>1</v>
       </c>
-      <c r="J15" s="21" t="n">
+      <c r="J15" s="36" t="n">
         <f aca="false">IF(D15=3,G15*1000/(SQRT(3)*Inputs!$B$6*H15*I15),G15*1000/(Inputs!$B$8*H15*I15))</f>
         <v>2.31481481481482</v>
       </c>
-      <c r="K15" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="L15" s="26" t="n">
+      <c r="K15" s="32" t="s">
+        <v>246</v>
+      </c>
+      <c r="L15" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="M15" s="18" t="n">
+      <c r="M15" s="34" t="n">
         <f aca="false">IF(K15="Y",G15*L15/I15,0)</f>
         <v>0</v>
       </c>
-      <c r="N15" s="18" t="n">
+      <c r="N15" s="34" t="n">
         <f aca="false">M15/H15</f>
         <v>0</v>
       </c>
-      <c r="O15" s="19" t="n">
+      <c r="O15" s="23" t="n">
         <f aca="false">IF(C15="Motor",Inputs!$B$17,Inputs!$B$18)</f>
         <v>1.25</v>
       </c>
-      <c r="P15" s="21" t="n">
+      <c r="P15" s="36" t="n">
         <f aca="false">J15*O15</f>
         <v>2.89351851851852</v>
       </c>
-      <c r="Q15" s="27" t="n">
+      <c r="Q15" s="41" t="n">
         <f aca="false">INDEX(Inputs!$H$5:$H$22,COUNTIF(Inputs!$H$5:$H$22,"&lt;"&amp;P15)+1)</f>
         <v>6</v>
       </c>
-      <c r="R15" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="S15" s="9" t="str">
+      <c r="R15" s="32" t="s">
+        <v>252</v>
+      </c>
+      <c r="S15" s="13" t="str">
         <f aca="false">IF(C15&lt;&gt;"Motor","-",IF(F15&gt;=Inputs!$B$26,"Star-Delta","DOL"))</f>
         <v>-</v>
       </c>
-      <c r="T15" s="28" t="n">
+      <c r="T15" s="42" t="n">
         <v>20</v>
       </c>
-      <c r="U15" s="21" t="n">
+      <c r="U15" s="36" t="n">
         <f aca="false">Q15/Inputs!$B$19</f>
         <v>6.89655172413793</v>
       </c>
-      <c r="V15" s="21" t="n">
+      <c r="V15" s="36" t="n">
         <f aca="false">INDEX(Inputs!$J$5:$J$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U15)+1)</f>
         <v>1.5</v>
       </c>
-      <c r="W15" s="27" t="n">
+      <c r="W15" s="41" t="n">
         <f aca="false">INDEX(Inputs!$K$5:$K$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U15)+1)</f>
         <v>22</v>
       </c>
-      <c r="X15" s="18" t="n">
+      <c r="X15" s="34" t="n">
         <f aca="false">INDEX(Inputs!$L$5:$L$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;U15)+1)*J15*T15/1000</f>
         <v>1.34259259259259</v>
       </c>
-      <c r="Y15" s="29" t="n">
+      <c r="Y15" s="43" t="n">
         <f aca="false">X15/IF(D15=3,Inputs!$B$6,Inputs!$B$8)</f>
         <v>0.00559413580246914</v>
       </c>
-      <c r="Z15" s="9" t="str">
+      <c r="Z15" s="13" t="str">
         <f aca="false">IF(Y15&lt;=IF(C15="Motor",Inputs!$B$20,Inputs!$B$21),"OK","EXCEEDS LIMIT - upsize cable")&amp;" - "&amp;"Spare way. Drawing: MCB 1P 6A"</f>
         <v>OK - Spare way. Drawing: MCB 1P 6A</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="G16" s="23" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="G16" s="37" t="n">
         <f aca="false">SUM(G5:G15)</f>
         <v>33.96</v>
       </c>
-      <c r="J16" s="31" t="n">
+      <c r="J16" s="21" t="n">
         <f aca="false">N16*1000/(SQRT(3)*Inputs!$B$6)</f>
         <v>38.821744459861</v>
       </c>
-      <c r="M16" s="23" t="n">
+      <c r="M16" s="37" t="n">
         <f aca="false">SUM(M5:M15)</f>
         <v>23.9026785714286</v>
       </c>
-      <c r="N16" s="23" t="n">
+      <c r="N16" s="37" t="n">
         <f aca="false">SUM(N5:N15)</f>
         <v>27.9051120448179</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="24" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="25" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="25" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="25" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="25" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="25" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="25" t="s">
-        <v>214</v>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="38" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="39" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="39" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="39" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="39" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="39" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="39" t="s">
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -4308,7 +5233,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
@@ -4316,617 +5241,617 @@
   <dimension ref="A1:D50"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="70"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>216</v>
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="B6" s="32" t="n">
+      <c r="D4" s="4" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="B6" s="45" t="n">
         <f aca="false">'Load Schedule'!G16</f>
         <v>33.96</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="B7" s="32" t="n">
+      <c r="D6" s="7" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="B7" s="45" t="n">
         <f aca="false">'Load Schedule'!M16</f>
         <v>23.9026785714286</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="B8" s="32" t="n">
+      <c r="D7" s="7" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="B8" s="45" t="n">
         <f aca="false">'Load Schedule'!N16</f>
         <v>27.9051120448179</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="B9" s="9" t="n">
+      <c r="D8" s="7" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="B9" s="13" t="n">
         <f aca="false">IFERROR(B7/B8,0)</f>
         <v>0.856569883433504</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+      <c r="C9" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="32" t="n">
+      <c r="B10" s="45" t="n">
         <f aca="false">B8*1000/(SQRT(3)*Inputs!$B$6)</f>
         <v>38.821744459861</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="B12" s="33" t="n">
+      <c r="D10" s="7" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="B12" s="46" t="n">
         <f aca="false">Inputs!$B$23</f>
         <v>0.25</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="B13" s="32" t="n">
+      <c r="C12" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="B13" s="45" t="n">
         <f aca="false">B10*(1+B12)</f>
         <v>48.5271805748262</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="B14" s="32" t="n">
+      <c r="D13" s="7" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="B14" s="45" t="n">
         <f aca="false">MAX('Load Schedule'!J5:J9)</f>
         <v>10.0467831848706</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="B15" s="32" t="n">
+      <c r="D14" s="7" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="B15" s="45" t="n">
         <f aca="false">B14*Inputs!$B$25</f>
         <v>20.0935663697412</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="B16" s="32" t="n">
+      <c r="D15" s="7" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="B16" s="45" t="n">
         <f aca="false">B10-B14+B15</f>
         <v>48.8685276447316</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="B18" s="32" t="n">
+      <c r="D16" s="7" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="B18" s="45" t="n">
         <f aca="false">INDEX(Inputs!$H$5:$H$22,COUNTIF(Inputs!$H$5:$H$22,"&lt;"&amp;B13)+1)</f>
         <v>50</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="B19" s="34" t="n">
+      <c r="D18" s="7" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="B19" s="47" t="n">
         <v>225</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="B20" s="35" t="n">
+      <c r="D19" s="7" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="B20" s="48" t="n">
         <f aca="false">B10/B19</f>
         <v>0.172541086488271</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
+      <c r="C20" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="32" t="n">
+      <c r="B21" s="45" t="n">
         <f aca="false">MAX(B18,63)</f>
         <v>63</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="B22" s="9" t="str">
+      <c r="D21" s="7" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="B22" s="13" t="str">
         <f aca="false">IF(B19&gt;=B18,"Adequate - oversized by "&amp;TEXT(B19/B18,"0.0")&amp;"x; acceptable if TNB connected load and metering CT are matched, otherwise reduce to recommended rating","UNDERSIZED - increase")</f>
         <v>Adequate - oversized by 4.5x; acceptable if TNB connected load and metering CT are matched, otherwise reduce to recommended rating</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="B24" s="12" t="n">
+      <c r="C22" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="B24" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="B25" s="32" t="n">
+      <c r="C24" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="B25" s="45" t="n">
         <f aca="false">B21/Inputs!$B$19</f>
         <v>72.4137931034483</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B26" s="32" t="n">
+      <c r="D25" s="7" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="B26" s="45" t="n">
         <f aca="false">INDEX(Inputs!$J$5:$J$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;B25)+1)</f>
         <v>16</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="B27" s="32" t="n">
+      <c r="D26" s="7" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="B27" s="45" t="n">
         <f aca="false">INDEX(Inputs!$K$5:$K$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;B25)+1)</f>
         <v>94</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="6"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="B28" s="32" t="n">
+      <c r="D27" s="7"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="B28" s="45" t="n">
         <f aca="false">INDEX(Inputs!$L$5:$L$19,COUNTIF(Inputs!$K$5:$K$19,"&lt;"&amp;B25)+1)*B13*B24/1000</f>
         <v>3.39690264023783</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="B29" s="35" t="n">
+      <c r="C28" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="B29" s="48" t="n">
         <f aca="false">B28/Inputs!$B$6</f>
         <v>0.00818530756683815</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="B30" s="9" t="str">
+      <c r="C29" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="B30" s="13" t="str">
         <f aca="false">IF(B29&lt;=Inputs!$B$20,"OK","EXCEEDS - upsize cable")</f>
         <v>OK</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D30" s="6"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-    </row>
-    <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>265</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="B33" s="32" t="n">
+      <c r="C30" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D30" s="7"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+    </row>
+    <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="B32" s="32" t="s">
+        <v>322</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="B33" s="45" t="n">
         <f aca="false">ROUNDUP(B8*(1+B12),0)</f>
         <v>35</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="B34" s="32" t="n">
+      <c r="D33" s="7" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="B34" s="45" t="n">
         <f aca="false">ROUNDUP(B6,0)</f>
         <v>34</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D34" s="6"/>
-    </row>
-    <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="B35" s="9" t="str">
+      <c r="D34" s="7"/>
+    </row>
+    <row r="35" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="B35" s="13" t="str">
         <f aca="false">IF(B33&lt;=100,"LV Commercial / Industrial (below 100 kVA class)","LV supply above 100 kVA - TNB may require CT metering")</f>
         <v>LV Commercial / Industrial (below 100 kVA class)</v>
       </c>
-      <c r="C35" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="B36" s="32" t="n">
+      <c r="C35" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="B36" s="45" t="n">
         <f aca="false">B7*Inputs!$B$29*Inputs!$B$30</f>
         <v>4302.48214285714</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D36" s="6" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="B37" s="32" t="n">
+      <c r="D36" s="7" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="B37" s="45" t="n">
         <f aca="false">B36*Inputs!$B$31</f>
         <v>2189.96341071429</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="B39" s="32" t="n">
+      <c r="C37" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="B39" s="45" t="n">
         <f aca="false">B8</f>
         <v>27.9051120448179</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D39" s="6" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="B40" s="32" t="n">
+      <c r="D39" s="7" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="B40" s="45" t="n">
         <f aca="false">SQRT(3)*Inputs!$B$6*B15/1000</f>
         <v>14.4432773109244</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D40" s="6" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="B41" s="32" t="n">
+      <c r="D40" s="7" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="B41" s="45" t="n">
         <f aca="false">B39-SQRT(3)*415*B14/1000+B40</f>
         <v>35.1267507002801</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D41" s="6" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="B42" s="32" t="n">
+      <c r="D41" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="B42" s="45" t="n">
         <f aca="false">MAX(B39*1.25,B41)</f>
         <v>35.1267507002801</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D42" s="6" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="B43" s="32" t="n">
+      <c r="D42" s="7" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="B43" s="45" t="n">
         <f aca="false">INDEX({10;20;30;40;50;60;80;100;125;150;200},COUNTIF({10;20;30;40;50;60;80;100;125;150;200},"&lt;"&amp;B42)+1)</f>
         <v>40</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D43" s="6" t="s">
-        <v>286</v>
+      <c r="D43" s="7" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="B45" s="36"/>
-      <c r="C45" s="36"/>
-      <c r="D45" s="36"/>
+      <c r="A45" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="37" t="s">
-        <v>287</v>
-      </c>
-      <c r="B46" s="37"/>
-      <c r="C46" s="37"/>
-      <c r="D46" s="37"/>
+      <c r="A46" s="50" t="s">
+        <v>344</v>
+      </c>
+      <c r="B46" s="50"/>
+      <c r="C46" s="50"/>
+      <c r="D46" s="50"/>
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="37" t="s">
-        <v>288</v>
-      </c>
-      <c r="B47" s="37"/>
-      <c r="C47" s="37"/>
-      <c r="D47" s="37"/>
+      <c r="A47" s="50" t="s">
+        <v>345</v>
+      </c>
+      <c r="B47" s="50"/>
+      <c r="C47" s="50"/>
+      <c r="D47" s="50"/>
     </row>
     <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="37" t="s">
-        <v>289</v>
-      </c>
-      <c r="B48" s="37"/>
-      <c r="C48" s="37"/>
-      <c r="D48" s="37"/>
+      <c r="A48" s="50" t="s">
+        <v>346</v>
+      </c>
+      <c r="B48" s="50"/>
+      <c r="C48" s="50"/>
+      <c r="D48" s="50"/>
     </row>
     <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="37" t="s">
-        <v>290</v>
-      </c>
-      <c r="B49" s="37"/>
-      <c r="C49" s="37"/>
-      <c r="D49" s="37"/>
+      <c r="A49" s="50" t="s">
+        <v>347</v>
+      </c>
+      <c r="B49" s="50"/>
+      <c r="C49" s="50"/>
+      <c r="D49" s="50"/>
     </row>
     <row r="50" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="37" t="s">
-        <v>291</v>
-      </c>
-      <c r="B50" s="37"/>
-      <c r="C50" s="37"/>
-      <c r="D50" s="37"/>
+      <c r="A50" s="50" t="s">
+        <v>348</v>
+      </c>
+      <c r="B50" s="50"/>
+      <c r="C50" s="50"/>
+      <c r="D50" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="6">
